--- a/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
+++ b/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
@@ -932,6 +932,11 @@
           <t>64233</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>64231</t>
@@ -14901,6 +14906,11 @@
           <t>64233</t>
         </is>
       </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T209" t="inlineStr">
         <is>
           <t>64231</t>
@@ -29543,6 +29553,11 @@
           <t>00:04.896</t>
         </is>
       </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -31068,6 +31083,11 @@
           <t>00:03.987</t>
         </is>
       </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>64412</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -36403,6 +36423,11 @@
           <t>00:03.738</t>
         </is>
       </c>
+      <c r="R523" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
@@ -37813,6 +37838,11 @@
           <t>00:07.829</t>
         </is>
       </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>64412</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -48929,6 +48959,11 @@
           <t>00:01.992</t>
         </is>
       </c>
+      <c r="R709" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="inlineStr">
@@ -55164,6 +55199,11 @@
           <t>64233</t>
         </is>
       </c>
+      <c r="S799" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
       <c r="T799" t="inlineStr">
         <is>
           <t>64231</t>
@@ -73080,6 +73120,11 @@
           <t>00:00.833</t>
         </is>
       </c>
+      <c r="R1061" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="1062">
       <c r="A1062" t="inlineStr">
@@ -87777,6 +87822,11 @@
           <t>00:02.130</t>
         </is>
       </c>
+      <c r="R1273" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" t="inlineStr">
@@ -92625,6 +92675,11 @@
       <c r="Q1341" t="inlineStr">
         <is>
           <t>00:01.468</t>
+        </is>
+      </c>
+      <c r="R1341" t="inlineStr">
+        <is>
+          <t>42444</t>
         </is>
       </c>
     </row>
@@ -96232,7 +96287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D346"/>
+  <dimension ref="A1:D349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103847,6 +103902,72 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>61249</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Alyssa</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>BULL</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>42444</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Anja</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>OSTERMAN</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>64412</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Alyson</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>MORSE</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
+++ b/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
@@ -1617,6 +1617,11 @@
           <t>51657</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>51688</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1682,6 +1687,11 @@
           <t>00:05.164</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>118806</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1812,6 +1822,11 @@
           <t>00:01.149</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1947,6 +1962,11 @@
           <t>00:10.880</t>
         </is>
       </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>64780</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2287,6 +2307,11 @@
           <t>01:24.735</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2692,6 +2717,11 @@
           <t>00:05.223</t>
         </is>
       </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>69075</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3232,6 +3262,11 @@
           <t>00:12.007</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>165767</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3437,6 +3472,11 @@
           <t>00:27.988</t>
         </is>
       </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4075,6 +4115,11 @@
       <c r="L52" t="n">
         <v>1</v>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>99812</t>
+        </is>
+      </c>
       <c r="X52" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -4944,6 +4989,11 @@
           <t>00:13.906</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5079,6 +5129,11 @@
           <t>00:19.876</t>
         </is>
       </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6019,6 +6074,11 @@
           <t>00:04.287</t>
         </is>
       </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>64558</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6419,6 +6479,11 @@
           <t>00:00.562</t>
         </is>
       </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6684,6 +6749,11 @@
           <t>01:29.247</t>
         </is>
       </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7543,6 +7613,11 @@
           <t>00:30.637</t>
         </is>
       </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7937,6 +8012,11 @@
           <t>00:50.095</t>
         </is>
       </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8601,6 +8681,11 @@
           <t>00:02.723</t>
         </is>
       </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9371,6 +9456,11 @@
           <t>00:11.153</t>
         </is>
       </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9501,6 +9591,11 @@
           <t>42841</t>
         </is>
       </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>42851</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10631,6 +10726,11 @@
           <t>00:00.922</t>
         </is>
       </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11481,6 +11581,11 @@
           <t>00:21.757</t>
         </is>
       </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
       <c r="S161" t="inlineStr">
         <is>
           <t>70016</t>
@@ -11746,6 +11851,11 @@
           <t>00:04.068</t>
         </is>
       </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S165" t="inlineStr">
         <is>
           <t>42488</t>
@@ -12031,6 +12141,11 @@
           <t>00:12.191</t>
         </is>
       </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>53066</t>
@@ -12871,6 +12986,11 @@
           <t>00:24.120</t>
         </is>
       </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -13146,6 +13266,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13861,6 +13986,11 @@
           <t>00:42.155</t>
         </is>
       </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14986,6 +15116,11 @@
           <t>51657</t>
         </is>
       </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>51688</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -15196,6 +15331,11 @@
           <t>00:05.322</t>
         </is>
       </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>118806</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15611,6 +15751,11 @@
           <t>00:07.862</t>
         </is>
       </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -15676,6 +15821,11 @@
           <t>00:13.845</t>
         </is>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>69075</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -16816,6 +16966,11 @@
           <t>03:55.547</t>
         </is>
       </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>64780</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -17071,6 +17226,11 @@
           <t>00:23.239</t>
         </is>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>165767</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -18116,6 +18276,11 @@
           <t>00:08.335</t>
         </is>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -18251,6 +18416,11 @@
           <t>00:21.513</t>
         </is>
       </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -18901,6 +19071,11 @@
           <t>05:37.397</t>
         </is>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -19161,6 +19336,11 @@
           <t>00:06.989</t>
         </is>
       </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>64558</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -19556,6 +19736,11 @@
           <t>00:03.381</t>
         </is>
       </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -19886,6 +20071,11 @@
           <t>00:28.013</t>
         </is>
       </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -20016,6 +20206,11 @@
           <t>04:25.614</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -20401,6 +20596,11 @@
           <t>05:18.362</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -21976,6 +22176,11 @@
           <t>00:13.872</t>
         </is>
       </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -22580,6 +22785,11 @@
           <t>00:14.225</t>
         </is>
       </c>
+      <c r="R324" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
       <c r="S324" t="inlineStr">
         <is>
           <t>70016</t>
@@ -23135,6 +23345,11 @@
           <t>00:04.489</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S332" t="inlineStr">
         <is>
           <t>42488</t>
@@ -23205,6 +23420,11 @@
           <t>00:07.931</t>
         </is>
       </c>
+      <c r="R333" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S333" t="inlineStr">
         <is>
           <t>53066</t>
@@ -23895,6 +24115,11 @@
           <t>00:32.317</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -24354,6 +24579,11 @@
           <t>00:50.139</t>
         </is>
       </c>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -25259,6 +25489,11 @@
           <t>45547</t>
         </is>
       </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>165767</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -25404,6 +25639,11 @@
           <t>00:55.912</t>
         </is>
       </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>54821</t>
+        </is>
+      </c>
       <c r="T364" t="inlineStr">
         <is>
           <t>68788</t>
@@ -25554,6 +25794,11 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
       <c r="U366" t="inlineStr">
         <is>
           <t>53472</t>
@@ -30208,6 +30453,16 @@
           <t>00:36.212</t>
         </is>
       </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
+      <c r="T434" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -30268,6 +30523,11 @@
           <t>03:02.258</t>
         </is>
       </c>
+      <c r="R435" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="U435" t="inlineStr">
         <is>
           <t>36153</t>
@@ -30588,6 +30848,11 @@
           <t>42881</t>
         </is>
       </c>
+      <c r="T439" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="U439" t="inlineStr">
         <is>
           <t>42452</t>
@@ -31993,6 +32258,11 @@
           <t>01:48.671</t>
         </is>
       </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -33673,6 +33943,11 @@
           <t>45547</t>
         </is>
       </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>165767</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -37003,6 +37278,11 @@
           <t>42881</t>
         </is>
       </c>
+      <c r="T531" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="U531" t="inlineStr">
         <is>
           <t>42452</t>
@@ -37213,6 +37493,16 @@
           <t>00:31.445</t>
         </is>
       </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
+      <c r="T534" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -41033,6 +41323,11 @@
           <t>00:06.348</t>
         </is>
       </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -41978,6 +42273,11 @@
           <t>00:04.787</t>
         </is>
       </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>118806</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="inlineStr">
@@ -45291,6 +45591,11 @@
           <t>00:04.093</t>
         </is>
       </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
@@ -45756,6 +46061,11 @@
           <t>00:34.002</t>
         </is>
       </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>53907</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
@@ -46220,6 +46530,11 @@
           <t>00:16.553</t>
         </is>
       </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>61440</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
@@ -46550,6 +46865,11 @@
           <t>00:01.472</t>
         </is>
       </c>
+      <c r="R673" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -46820,6 +47140,11 @@
           <t>00:16.376</t>
         </is>
       </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
@@ -48095,6 +48420,11 @@
           <t>00:13.910</t>
         </is>
       </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>46104</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="inlineStr">
@@ -48225,6 +48555,11 @@
           <t>00:00.236</t>
         </is>
       </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="inlineStr">
@@ -50234,6 +50569,11 @@
           <t>00:06.526</t>
         </is>
       </c>
+      <c r="R728" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
@@ -50299,6 +50639,11 @@
           <t>00:13.281</t>
         </is>
       </c>
+      <c r="R729" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" t="inlineStr">
@@ -50499,6 +50844,11 @@
           <t>00:02.280</t>
         </is>
       </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -52398,6 +52748,11 @@
           <t>00:05.264</t>
         </is>
       </c>
+      <c r="S760" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -52463,6 +52818,11 @@
           <t>00:17.694</t>
         </is>
       </c>
+      <c r="R761" t="inlineStr">
+        <is>
+          <t>54821</t>
+        </is>
+      </c>
     </row>
     <row r="762">
       <c r="A762" t="inlineStr">
@@ -52813,6 +53173,11 @@
           <t>00:02.118</t>
         </is>
       </c>
+      <c r="R766" t="inlineStr">
+        <is>
+          <t>61392</t>
+        </is>
+      </c>
       <c r="S766" t="inlineStr">
         <is>
           <t>64524</t>
@@ -54283,6 +54648,11 @@
           <t>00:01.551</t>
         </is>
       </c>
+      <c r="R787" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S787" t="inlineStr">
         <is>
           <t>53066</t>
@@ -54553,6 +54923,11 @@
           <t>00:06.336</t>
         </is>
       </c>
+      <c r="S791" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="792">
       <c r="A792" t="inlineStr">
@@ -55353,6 +55728,11 @@
           <t>03:40.049</t>
         </is>
       </c>
+      <c r="R801" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
     </row>
     <row r="802">
       <c r="A802" t="inlineStr">
@@ -55564,6 +55944,11 @@
           <t>00:05.044</t>
         </is>
       </c>
+      <c r="R804" t="inlineStr">
+        <is>
+          <t>64780</t>
+        </is>
+      </c>
     </row>
     <row r="805">
       <c r="A805" t="inlineStr">
@@ -55698,6 +56083,11 @@
           <t>00:06.161</t>
         </is>
       </c>
+      <c r="R806" t="inlineStr">
+        <is>
+          <t>69075</t>
+        </is>
+      </c>
     </row>
     <row r="807">
       <c r="A807" t="inlineStr">
@@ -56110,6 +56500,11 @@
           <t>00:02.704</t>
         </is>
       </c>
+      <c r="R812" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
@@ -56527,6 +56922,11 @@
           <t>00:15.256</t>
         </is>
       </c>
+      <c r="R818" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
@@ -57098,6 +57498,11 @@
           <t>00:12.950</t>
         </is>
       </c>
+      <c r="S826" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -58930,6 +59335,11 @@
           <t>00:03.176</t>
         </is>
       </c>
+      <c r="R852" t="inlineStr">
+        <is>
+          <t>64558</t>
+        </is>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="inlineStr">
@@ -59584,6 +59994,11 @@
       <c r="L862" t="n">
         <v>1</v>
       </c>
+      <c r="R862" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
       <c r="X862" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -59707,6 +60122,11 @@
           <t>03:20.282</t>
         </is>
       </c>
+      <c r="R864" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="S864" t="inlineStr">
         <is>
           <t>42488</t>
@@ -59980,6 +60400,11 @@
           <t>03:26.393</t>
         </is>
       </c>
+      <c r="R868" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S868" t="inlineStr">
         <is>
           <t>53066</t>
@@ -60119,6 +60544,11 @@
           <t>03:39.756</t>
         </is>
       </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -60516,6 +60946,11 @@
           <t>03:33.031</t>
         </is>
       </c>
+      <c r="R876" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="inlineStr">
@@ -61109,6 +61544,11 @@
           <t>03:59.428</t>
         </is>
       </c>
+      <c r="R885" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="inlineStr">
@@ -62335,6 +62775,11 @@
           <t>42841</t>
         </is>
       </c>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>42851</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
@@ -62896,6 +63341,11 @@
           <t>03:40.206</t>
         </is>
       </c>
+      <c r="R910" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
     </row>
     <row r="911">
       <c r="A911" t="inlineStr">
@@ -64522,6 +64972,11 @@
           <t>46671</t>
         </is>
       </c>
+      <c r="S933" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="934">
       <c r="A934" t="inlineStr">
@@ -66351,6 +66806,11 @@
           <t>00:06.704</t>
         </is>
       </c>
+      <c r="R960" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
     </row>
     <row r="961">
       <c r="A961" t="inlineStr">
@@ -68176,6 +68636,11 @@
           <t>00:04.721</t>
         </is>
       </c>
+      <c r="R987" t="inlineStr">
+        <is>
+          <t>118806</t>
+        </is>
+      </c>
     </row>
     <row r="988">
       <c r="A988" t="inlineStr">
@@ -69111,6 +69576,11 @@
           <t>00:00.844</t>
         </is>
       </c>
+      <c r="R1001" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="1002">
       <c r="A1002" t="inlineStr">
@@ -71121,6 +71591,11 @@
           <t>00:10.463</t>
         </is>
       </c>
+      <c r="R1031" t="inlineStr">
+        <is>
+          <t>61440</t>
+        </is>
+      </c>
     </row>
     <row r="1032">
       <c r="A1032" t="inlineStr">
@@ -71186,6 +71661,11 @@
           <t>00:27.544</t>
         </is>
       </c>
+      <c r="R1032" t="inlineStr">
+        <is>
+          <t>53907</t>
+        </is>
+      </c>
     </row>
     <row r="1033">
       <c r="A1033" t="inlineStr">
@@ -72396,6 +72876,11 @@
           <t>00:14.678</t>
         </is>
       </c>
+      <c r="R1050" t="inlineStr">
+        <is>
+          <t>46104</t>
+        </is>
+      </c>
     </row>
     <row r="1051">
       <c r="A1051" t="inlineStr">
@@ -72666,6 +73151,11 @@
           <t>00:01.361</t>
         </is>
       </c>
+      <c r="R1054" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1055">
       <c r="A1055" t="inlineStr">
@@ -72985,6 +73475,11 @@
       <c r="L1059" t="n">
         <v>1</v>
       </c>
+      <c r="R1059" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
       <c r="X1059" t="inlineStr">
         <is>
           <t>DNS</t>
@@ -73655,6 +74150,11 @@
           <t>00:43.866</t>
         </is>
       </c>
+      <c r="R1069" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" t="inlineStr">
@@ -74470,6 +74970,11 @@
           <t>00:00.968</t>
         </is>
       </c>
+      <c r="R1081" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1082">
       <c r="A1082" t="inlineStr">
@@ -75345,6 +75850,11 @@
           <t>00:03.315</t>
         </is>
       </c>
+      <c r="R1094" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="1095">
       <c r="A1095" t="inlineStr">
@@ -75955,6 +76465,11 @@
           <t>00:04.076</t>
         </is>
       </c>
+      <c r="S1103" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -76365,6 +76880,11 @@
           <t>00:02.000</t>
         </is>
       </c>
+      <c r="R1109" t="inlineStr">
+        <is>
+          <t>61392</t>
+        </is>
+      </c>
       <c r="S1109" t="inlineStr">
         <is>
           <t>64524</t>
@@ -76640,6 +77160,11 @@
           <t>00:13.765</t>
         </is>
       </c>
+      <c r="R1113" t="inlineStr">
+        <is>
+          <t>54821</t>
+        </is>
+      </c>
     </row>
     <row r="1114">
       <c r="A1114" t="inlineStr">
@@ -77280,6 +77805,11 @@
           <t>00:05.022</t>
         </is>
       </c>
+      <c r="S1122" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
     </row>
     <row r="1123">
       <c r="A1123" t="inlineStr">
@@ -77690,6 +78220,11 @@
           <t>00:02.677</t>
         </is>
       </c>
+      <c r="R1128" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S1128" t="inlineStr">
         <is>
           <t>53066</t>
@@ -79985,6 +80520,11 @@
           <t>00:00.540</t>
         </is>
       </c>
+      <c r="R1161" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="1162">
       <c r="A1162" t="inlineStr">
@@ -80459,6 +80999,11 @@
           <t>00:35.183</t>
         </is>
       </c>
+      <c r="R1168" t="inlineStr">
+        <is>
+          <t>61392</t>
+        </is>
+      </c>
       <c r="S1168" t="inlineStr">
         <is>
           <t>64524</t>
@@ -81030,6 +81575,11 @@
           <t>00:02.518</t>
         </is>
       </c>
+      <c r="S1176" t="inlineStr">
+        <is>
+          <t>36411</t>
+        </is>
+      </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
@@ -84487,6 +85037,11 @@
           <t>00:00.489</t>
         </is>
       </c>
+      <c r="R1225" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" t="inlineStr">
@@ -85594,6 +86149,11 @@
           <t>00:00.954</t>
         </is>
       </c>
+      <c r="R1241" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="inlineStr">
@@ -86011,6 +86571,11 @@
           <t>00:03.493</t>
         </is>
       </c>
+      <c r="R1247" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" t="inlineStr">
@@ -86417,6 +86982,11 @@
           <t>00:00.672</t>
         </is>
       </c>
+      <c r="R1253" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
       <c r="S1253" t="inlineStr">
         <is>
           <t>53066</t>
@@ -87688,6 +88258,11 @@
           <t>00:01.474</t>
         </is>
       </c>
+      <c r="R1271" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="inlineStr">
@@ -88882,6 +89457,11 @@
           <t>00:03.573</t>
         </is>
       </c>
+      <c r="R1288" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="inlineStr">
@@ -89016,6 +89596,11 @@
           <t>00:04.860</t>
         </is>
       </c>
+      <c r="R1290" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
     </row>
     <row r="1291">
       <c r="A1291" t="inlineStr">
@@ -90177,6 +90762,11 @@
           <t>69409</t>
         </is>
       </c>
+      <c r="S1306" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
       <c r="U1306" t="inlineStr">
         <is>
           <t>53472</t>
@@ -92404,6 +92994,11 @@
           <t>00:43.920</t>
         </is>
       </c>
+      <c r="R1337" t="inlineStr">
+        <is>
+          <t>53907</t>
+        </is>
+      </c>
       <c r="S1337" t="inlineStr">
         <is>
           <t>53906</t>
@@ -94072,6 +94667,11 @@
           <t>00:14.471</t>
         </is>
       </c>
+      <c r="R1361" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
       <c r="S1361" t="inlineStr">
         <is>
           <t>42260</t>
@@ -94360,6 +94960,11 @@
           <t>00:00.347</t>
         </is>
       </c>
+      <c r="R1365" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
       <c r="U1365" t="inlineStr">
         <is>
           <t>36153</t>
@@ -94929,6 +95534,11 @@
           <t>42881</t>
         </is>
       </c>
+      <c r="T1372" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
       <c r="U1372" t="inlineStr">
         <is>
           <t>42452</t>
@@ -95667,6 +96277,11 @@
       <c r="P1382" t="inlineStr">
         <is>
           <t>01:40.175</t>
+        </is>
+      </c>
+      <c r="S1382" t="inlineStr">
+        <is>
+          <t>36164</t>
         </is>
       </c>
     </row>
@@ -96287,7 +96902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D349"/>
+  <dimension ref="A1:D382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -103968,6 +104583,732 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Dan</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>DRAHOKOUPIL</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>36160</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Ilya</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>PERVUKHIN</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>36164</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Natalia</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>PODOLSKAIA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>42144</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Aleksandr</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SERGEEV</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>42548</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Khaled</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>HOUCINE</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>42851</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Morten</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>GRAVERSEN</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>45529</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Robert Michael James</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CLARKE</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>46104</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Satyam</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>MAHARAJ</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>47336</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SHURINKIN</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>51670</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>KLIMAVA</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>51688</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Anastasiya</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>BABOK</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>52228</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Aleksey</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>MOCHALOV</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>HEFNER</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>53065</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Christopher</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>MILLER</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>53428</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Oleg</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SINIAVIN</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>53907</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Si Cheng</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>NG</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>54821</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Man Tou</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>CHE</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>60077</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Chi Chong</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>LAM</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>61392</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SCOTT</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>61440</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Inaocha Devi</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>MAYANGLANBAM</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>64558</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Jarett</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>KENKE</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>64780</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Baies</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>CRISTIAN</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>69075</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Marlen</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SEITYAGYAEV</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>75474</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>FRIEND CHUNG</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>80427</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Gyanjit Singh</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>ARAMBAM</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>83311</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Seojun</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>PARK</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>99812</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Muhammad Abubakar</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>DURRANI</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>103245</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Ching Ching Singh</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>ARAMBAM</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>106159</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Seongwoo</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SHIN</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>118806</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Ran</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>CHOI</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>165553</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Tsz Chung</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>CHEUNG</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>165767</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Ulices Josue</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>GONZALEZ MELENDEZ</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
+++ b/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
@@ -9456,11 +9456,6 @@
           <t>00:11.153</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -22176,11 +22171,6 @@
           <t>00:13.872</t>
         </is>
       </c>
-      <c r="S315" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -52748,11 +52738,6 @@
           <t>00:05.264</t>
         </is>
       </c>
-      <c r="S760" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -57498,11 +57483,6 @@
           <t>00:12.950</t>
         </is>
       </c>
-      <c r="S826" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
@@ -76465,11 +76445,6 @@
           <t>00:04.076</t>
         </is>
       </c>
-      <c r="S1103" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
     </row>
     <row r="1104">
       <c r="A1104" t="inlineStr">
@@ -81573,11 +81548,6 @@
       <c r="Q1176" t="inlineStr">
         <is>
           <t>00:02.518</t>
-        </is>
-      </c>
-      <c r="S1176" t="inlineStr">
-        <is>
-          <t>36411</t>
         </is>
       </c>
     </row>

--- a/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
+++ b/events/Welland_2013_JWCH/Welland_2013_JWCH_Results.xlsx
@@ -1232,6 +1232,11 @@
           <t>42352</t>
         </is>
       </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27848,6 +27853,11 @@
           <t>02:00.900</t>
         </is>
       </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -35288,6 +35298,11 @@
           <t>02:07.449</t>
         </is>
       </c>
+      <c r="R502" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -41988,6 +42003,11 @@
           <t>00:46.236</t>
         </is>
       </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
@@ -55487,6 +55507,11 @@
           <t>42352</t>
         </is>
       </c>
+      <c r="T798" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="799">
       <c r="A799" t="inlineStr">
@@ -68146,6 +68171,11 @@
           <t>00:42.523</t>
         </is>
       </c>
+      <c r="R980" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="981">
       <c r="A981" t="inlineStr">
@@ -82240,6 +82270,11 @@
           <t>00:41.034</t>
         </is>
       </c>
+      <c r="R1186" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
     </row>
     <row r="1187">
       <c r="A1187" t="inlineStr">
@@ -91897,6 +91932,11 @@
       <c r="P1322" t="inlineStr">
         <is>
           <t>01:52.554</t>
+        </is>
+      </c>
+      <c r="R1322" t="inlineStr">
+        <is>
+          <t>42844</t>
         </is>
       </c>
     </row>
@@ -96872,7 +96912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D382"/>
+  <dimension ref="A1:D383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -105279,6 +105319,28 @@
         </is>
       </c>
     </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>42844</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>JØRGENSEN</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
